--- a/backups/tabla_maestra_hierbas_app_editada.xlsx
+++ b/backups/tabla_maestra_hierbas_app_editada.xlsx
@@ -801,7 +801,7 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>Amargón (Diente de león)</t>
+          <t>Amargón</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
